--- a/research/PINS/Reports/PINS_DCF_Model.xlsx
+++ b/research/PINS/Reports/PINS_DCF_Model.xlsx
@@ -2304,9 +2304,10 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B12" s="5">
         <v>-343.064</v>
